--- a/기존 파일_2023/question_list_2023.xlsx
+++ b/기존 파일_2023/question_list_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Claude\Projects\인식DB 대시보드_\기존 파일_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC10F706-1ED0-422A-933B-598C800CB556}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01557585-FFED-4843-AD7D-FEED414CDA1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12120" windowHeight="17295" xr2:uid="{4ADDA054-9EA2-4C72-A451-6E4A781EA472}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="202">
   <si>
     <t>category_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -724,6 +724,14 @@
   </si>
   <si>
     <t>패널 기본정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>formula</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상적인 사무실 출근일수' 에서 응답한 보기의 숫자 ex. 주5일 선택일 경우 숫자 '5'로 환산</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -770,8 +778,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,10 +1099,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB2BF7B-5452-4F87-979E-046ADCBA4346}">
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1104,8 +1115,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1116,7 +1130,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1127,7 +1141,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1138,7 +1152,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1149,7 +1163,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1160,7 +1174,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1171,7 +1185,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1182,7 +1196,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1196,7 +1210,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1210,7 +1224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1224,7 +1238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1252,7 +1266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1266,7 +1280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1280,7 +1294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1294,7 +1308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1308,7 +1322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1322,7 +1336,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1336,7 +1350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1350,7 +1364,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1358,13 +1372,16 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1372,13 +1389,13 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1386,13 +1403,13 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1400,13 +1417,13 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1414,13 +1431,13 @@
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1428,27 +1445,27 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
         <v>39</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1456,13 +1473,13 @@
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1470,13 +1487,13 @@
         <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1484,13 +1501,13 @@
         <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1498,13 +1515,13 @@
         <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1512,10 +1529,10 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1526,10 +1543,10 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1540,10 +1557,10 @@
         <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1554,10 +1571,10 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1568,10 +1585,10 @@
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1582,10 +1599,10 @@
         <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1596,10 +1613,10 @@
         <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1610,10 +1627,10 @@
         <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1624,10 +1641,10 @@
         <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1635,13 +1652,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1652,10 +1669,10 @@
         <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1666,10 +1683,10 @@
         <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1680,10 +1697,10 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1694,10 +1711,10 @@
         <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1708,10 +1725,10 @@
         <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1722,10 +1739,10 @@
         <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1736,10 +1753,10 @@
         <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1750,10 +1767,10 @@
         <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1764,21 +1781,24 @@
         <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1786,10 +1806,10 @@
         <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1797,10 +1817,10 @@
         <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1808,10 +1828,10 @@
         <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1819,10 +1839,10 @@
         <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1830,10 +1850,10 @@
         <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1841,10 +1861,10 @@
         <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1852,10 +1872,10 @@
         <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1863,10 +1883,10 @@
         <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1874,10 +1894,10 @@
         <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1885,10 +1905,10 @@
         <v>104</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1896,10 +1916,10 @@
         <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1907,10 +1927,10 @@
         <v>104</v>
       </c>
       <c r="C63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1918,24 +1938,21 @@
         <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1946,10 +1963,10 @@
         <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1960,10 +1977,10 @@
         <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1974,10 +1991,10 @@
         <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1988,10 +2005,10 @@
         <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D69" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -2002,10 +2019,10 @@
         <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -2016,10 +2033,10 @@
         <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D71" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -2030,10 +2047,10 @@
         <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -2044,10 +2061,10 @@
         <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -2058,10 +2075,10 @@
         <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -2072,10 +2089,10 @@
         <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -2086,10 +2103,10 @@
         <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -2097,13 +2114,13 @@
         <v>132</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2114,10 +2131,10 @@
         <v>160</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2128,10 +2145,10 @@
         <v>160</v>
       </c>
       <c r="C79" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D79" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2142,10 +2159,10 @@
         <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2156,10 +2173,10 @@
         <v>160</v>
       </c>
       <c r="C81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D81" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2170,10 +2187,10 @@
         <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D82" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2184,10 +2201,10 @@
         <v>160</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D83" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2198,10 +2215,10 @@
         <v>160</v>
       </c>
       <c r="C84" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2212,10 +2229,10 @@
         <v>160</v>
       </c>
       <c r="C85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2226,10 +2243,10 @@
         <v>160</v>
       </c>
       <c r="C86" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D86" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2237,13 +2254,13 @@
         <v>132</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C87" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D87" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2254,10 +2271,10 @@
         <v>181</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2268,10 +2285,10 @@
         <v>181</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2282,10 +2299,10 @@
         <v>181</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2296,10 +2313,10 @@
         <v>181</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2310,24 +2327,24 @@
         <v>181</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
         <v>181</v>
       </c>
       <c r="C93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D93" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2338,10 +2355,10 @@
         <v>181</v>
       </c>
       <c r="C94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2352,10 +2369,10 @@
         <v>181</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2366,14 +2383,29 @@
         <v>181</v>
       </c>
       <c r="C96" t="s">
+        <v>190</v>
+      </c>
+      <c r="D96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" t="s">
         <v>191</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D97" t="s">
         <v>180</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>